--- a/config/tables/gas.modifier.xlsx
+++ b/config/tables/gas.modifier.xlsx
@@ -1,135 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Bevy\BevyProjects\bevy_gas\config\tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Modifier" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modifier" sheetId="1" r:id="Rd5bd83f64cdb4344"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>effect_id</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>attribute</t>
-  </si>
-  <si>
-    <t>operation</t>
-  </si>
-  <si>
-    <t>magnitude_kind</t>
-  </si>
-  <si>
-    <t>base</t>
-  </si>
-  <si>
-    <t>per_level</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int#range=[1,1000000]</t>
-  </si>
-  <si>
-    <t>int#ref=gas.TbEffect</t>
-  </si>
-  <si>
-    <t>int#range=[0,1000000]</t>
-  </si>
-  <si>
-    <t>string#ref=gas.TbAttribute</t>
-  </si>
-  <si>
-    <t>gas.ModifierOperation</t>
-  </si>
-  <si>
-    <t>gas.MagnitudeKind</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>Unique modifier identifier.</t>
-  </si>
-  <si>
-    <t>Owning effect identifier.</t>
-  </si>
-  <si>
-    <t>Modifier order within the effect.</t>
-  </si>
-  <si>
-    <t>Modified attribute name.</t>
-  </si>
-  <si>
-    <t>Attribute modification operation.</t>
-  </si>
-  <si>
-    <t>Flat value or level-dependent linear value.</t>
-  </si>
-  <si>
-    <t>Magnitude at ability level one.</t>
-  </si>
-  <si>
-    <t>Magnitude added for each level above one. Zero for Flat.</t>
-  </si>
-  <si>
-    <t>Mana</t>
-  </si>
-  <si>
-    <t>Add</t>
-  </si>
-  <si>
-    <t>Flat</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>LinearLevel</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1268,185 +1147,154 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="9" width="23" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" ht="52" customHeight="1" spans="1:9">
-      <c r="A2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" ht="66" customHeight="1" spans="1:9">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1" spans="1:9">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6">
-        <v>20101</v>
-      </c>
-      <c r="C5" s="6">
-        <v>2001</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="7">
-        <v>-20</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="25" customHeight="1" spans="1:9">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6">
-        <v>20301</v>
-      </c>
-      <c r="C6" s="6">
-        <v>2003</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="7">
-        <v>-100</v>
-      </c>
-      <c r="I6" s="7">
-        <v>-20</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="F5:F6">
-      <formula1>"Add,PercentAdd,Multiply,Override"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="G5:G6">
-      <formula1>"Flat,LinearLevel"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="9" width="23" customWidth="1"/>
+    <x:col min="3" max="3" width="23" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>attribute</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>operation</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>magnitude_kind</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>base</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="str">
+        <x:v>per_level</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="52" customHeight="1">
+      <x:c r="A2" s="2" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>int#range=[1,1000000]</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>string#ref=gas.TbAttribute</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>gas.ModifierOperation</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="str">
+        <x:v>gas.MagnitudeKind</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="25" customHeight="1">
+      <x:c r="A3" s="3" t="str">
+        <x:v>##group</x:v>
+      </x:c>
+      <x:c r="B3" s="3"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="66" customHeight="1">
+      <x:c r="A4" s="4" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>Unique modifier identifier.</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>Modified attribute name.</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>Attribute modification operation.</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>Flat value or level-dependent linear value.</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>Magnitude at ability level one.</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="str">
+        <x:v>Magnitude added for each level above one. Zero for Flat.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="25" customHeight="1">
+      <x:c r="A5" s="5"/>
+      <x:c r="B5" s="6" t="n">
+        <x:v>20101</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="str">
+        <x:v>Mana</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="str">
+        <x:v>Flat</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="n">
+        <x:v>-20</x:v>
+      </x:c>
+      <x:c r="G5" s="7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="A6" s="5"/>
+      <x:c r="B6" s="6" t="n">
+        <x:v>20301</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>Health</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="str">
+        <x:v>LinearLevel</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="n">
+        <x:v>-100</x:v>
+      </x:c>
+      <x:c r="G6" s="7" t="n">
+        <x:v>-20</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="D5:D6">
+      <x:formula1>"Add,PercentAdd,Multiply,Override"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E6">
+      <x:formula1>"Flat,LinearLevel"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>